--- a/templates/excel/reward-species-declaration.xlsx
+++ b/templates/excel/reward-species-declaration.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Long_Tail_Schedule" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Unit_Fund_Eligibility" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Renegotiation_Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="_metadata" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="_metadata" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -662,12 +662,12 @@
   </sheetData>
   <conditionalFormatting sqref="C2:E1000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ROUND(SUM($C2:$E2),3)&lt;&gt;1</formula>
+      <formula>AND(COUNT($C2:$E2)&gt;0,ROUND(SUM($C2:$E2),3)&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I1000">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ROUND(SUM($G2:$I2),3)&lt;&gt;1</formula>
+      <formula>AND(COUNT($G2:$I2)&gt;0,ROUND(SUM($G2:$I2),3)&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -902,167 +902,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># reward-species-declaration.xlsx</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Per-partner compensation contract. Records reward species, base amount, variable weights, output multiplier, bonus splits, long-tail entitlement schedule, and renegotiation history.</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>For organisations &lt;20 partners: ONE workbook with one sheet per partner. For larger orgs: one workbook per partner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UPDATED BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>- Manual at onboarding (Skill Pack S3 §4.1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- Manual at renegotiation (Skill Pack S3 §4.1 renegotiation flow).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- Routine R4 (Quarterly Long-Tail Settlement) updates Long_Tail_Schedule total_settled_to_date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REVIEWED BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Quarterly partner check-in (Skill Pack S5 §4.6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- Variable weights (Base_Variable_Split columns C+D+E) MUST sum to 1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- Bonus splits (G+H+I) MUST sum to 1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>- Conditional formatting flags violations in red.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Column F (output_multiplier) is NOT part of the variable-weight sum; it is a free-running multiplier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>- Override fields without a signed renegotiation flow per Skill Pack S3 §4.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>- Bypass the jurisdiction field; legal touchpoints depend on it (see governance/EU-AI-ACT.md and docs/06-when-to-call-a-lawyer.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>- Alter Long_Tail_Schedule retroactively without a new Renegotiation_Log entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>- Activate Unit_Fund_Eligibility before Gen 2 (sheet is password-protected by design).</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X2</t>
         </is>
       </c>
     </row>
@@ -1077,66 +976,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># reward-species-declaration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>Per-partner compensation contract. Records reward species, base amount, variable weights, output multiplier, bonus splits, long-tail entitlement schedule, and renegotiation history.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X2</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>For organisations &lt;20 partners: ONE workbook with one sheet per partner. For larger orgs: one workbook per partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UPDATED BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- Manual at onboarding (Skill Pack S3 §4.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- Manual at renegotiation (Skill Pack S3 §4.1 renegotiation flow).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- Routine R4 (Quarterly Long-Tail Settlement) updates Long_Tail_Schedule total_settled_to_date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REVIEWED BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Quarterly partner check-in (Skill Pack S5 §4.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- Variable weights (Base_Variable_Split columns C+D+E) MUST sum to 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- Bonus splits (G+H+I) MUST sum to 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Conditional formatting flags violations in red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Column F (output_multiplier) is NOT part of the variable-weight sum; it is a free-running multiplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>- Override fields without a signed renegotiation flow per Skill Pack S3 §4.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>- Bypass the jurisdiction field; legal touchpoints depend on it (see governance/EU-AI-ACT.md and docs/06-when-to-call-a-lawyer.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>- Alter Long_Tail_Schedule retroactively without a new Renegotiation_Log entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Activate Unit_Fund_Eligibility before Gen 2 (sheet is password-protected by design).</t>
         </is>
       </c>
     </row>

--- a/templates/excel/reward-species-declaration.xlsx
+++ b/templates/excel/reward-species-declaration.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -579,50 +579,56 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>reward_species</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>base_amount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>variable_weight_personal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variable_weight_team</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>variable_weight_company</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>output_multiplier</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bonus_split_personal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>bonus_split_team</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bonus_split_company</t>
         </is>
@@ -631,47 +637,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.34</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.33</v>
       </c>
       <c r="I2" t="n">
         <v>0.33</v>
       </c>
+      <c r="J2" t="n">
+        <v>0.33</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:E1000">
+  <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(COUNT($C2:$E2)&gt;0,ROUND(SUM($C2:$E2),3)&lt;&gt;1)</formula>
+      <formula>AND(COUNT($D2:$F2)&gt;0,ROUND(SUM($D2:$F2),3)&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I1000">
+  <conditionalFormatting sqref="H2:J1000">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(COUNT($G2:$I2)&gt;0,ROUND(SUM($G2:$I2),3)&lt;&gt;1)</formula>
+      <formula>AND(COUNT($H2:$J2)&gt;0,ROUND(SUM($H2:$J2),3)&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"eat-what-you-kill,lockstep,hybrid"</formula1>
     </dataValidation>
   </dataValidations>
@@ -685,50 +696,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>output_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>partner_share_pct</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>settlement_period</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>total_settled_to_date</t>
         </is>
@@ -737,33 +754,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>[SAMPLE]OL-20260212-014</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Acme contract — 3yr ARR</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2029-03-31</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -976,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1070,71 +1092,88 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
+          <t>SCHEMA (ADR-005)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- Variable weights (Base_Variable_Split columns C+D+E) MUST sum to 1.0.</t>
+          <t>- Base_Variable_Split and Long_Tail_Schedule each carry a LEADING partner_id column (A, format P-NNN) that joins Partner_Profile column A. Single shared sheets, one row per partner (Base_Variable_Split) / per partner-artifact (Long_Tail_Schedule). R1/R3/R4 lookups join on partner_id.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- Bonus splits (G+H+I) MUST sum to 1.0.</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Conditional formatting flags violations in red.</t>
+          <t>VALIDATION</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>- Column F (output_multiplier) is NOT part of the variable-weight sum; it is a free-running multiplier.</t>
+          <t>- Variable weights (Base_Variable_Split columns D+E+F) MUST sum to 1.0.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Bonus splits (H+I+J) MUST sum to 1.0.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DO NOT</t>
+          <t>- Conditional formatting flags violations in red.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>- Override fields without a signed renegotiation flow per Skill Pack S3 §4.1.</t>
+          <t>- Column G (output_multiplier) is NOT part of the variable-weight sum; it is a free-running multiplier.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>- Bypass the jurisdiction field; legal touchpoints depend on it (see governance/EU-AI-ACT.md and docs/06-when-to-call-a-lawyer.md).</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>- Alter Long_Tail_Schedule retroactively without a new Renegotiation_Log entry.</t>
+          <t>DO NOT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>- Override fields without a signed renegotiation flow per Skill Pack S3 §4.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- Bypass the jurisdiction field; legal touchpoints depend on it (see governance/EU-AI-ACT.md and docs/06-when-to-call-a-lawyer.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Alter Long_Tail_Schedule retroactively without a new Renegotiation_Log entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>- Activate Unit_Fund_Eligibility before Gen 2 (sheet is password-protected by design).</t>
         </is>
